--- a/training/整体培训计划与完整度.xlsx
+++ b/training/整体培训计划与完整度.xlsx
@@ -72,7 +72,8 @@
     <t>256 课时</t>
   </si>
   <si>
-    <t>6 门（ROS2:20、视觉:12、语音&amp;大模型:6、SLAM:7、机械臂:7、综合应用:9）</t>
+    <t>6 门（ROS2:20、视觉:12、语音&amp;大模型:6、SLAM:7、机械臂:7、综合应用:9）
+其中：ROS2的传感器部分适用于实验箱B2，SLAM部分仅适用于小车C1</t>
   </si>
   <si>
     <t>具身智能实验箱B2
